--- a/code/data/combined/cmb+dmul-lcdm-free.xlsx
+++ b/code/data/combined/cmb+dmul-lcdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39213914.00024605</v>
+        <v>44425444.09731483</v>
       </c>
       <c r="C2" t="n">
-        <v>-134286934.5381636</v>
+        <v>-148685611.423977</v>
       </c>
       <c r="D2" t="n">
-        <v>40645477.10335258</v>
+        <v>46689835.9911103</v>
       </c>
       <c r="E2" t="n">
-        <v>-410392.903729221</v>
+        <v>-468237.0929738093</v>
       </c>
       <c r="F2" t="n">
-        <v>-1418702.45083992</v>
+        <v>-1421460.028066205</v>
       </c>
       <c r="G2" t="n">
-        <v>882064.676976625</v>
+        <v>1050448.297797226</v>
       </c>
       <c r="H2" t="n">
-        <v>-2580705.56236195</v>
+        <v>-2936361.213968822</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134286934.5382065</v>
+        <v>-148685611.4238889</v>
       </c>
       <c r="C3" t="n">
-        <v>887991069.1101446</v>
+        <v>895782919.2517341</v>
       </c>
       <c r="D3" t="n">
-        <v>-89476835.98502241</v>
+        <v>-111911249.0018322</v>
       </c>
       <c r="E3" t="n">
-        <v>15741702.57410179</v>
+        <v>16344774.50351323</v>
       </c>
       <c r="F3" t="n">
-        <v>6695175.62384861</v>
+        <v>6648185.514448351</v>
       </c>
       <c r="G3" t="n">
-        <v>-3840600.547945131</v>
+        <v>-4444658.216509027</v>
       </c>
       <c r="H3" t="n">
-        <v>7957657.046586648</v>
+        <v>8986371.166766221</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40645477.10334785</v>
+        <v>46689835.99112028</v>
       </c>
       <c r="C4" t="n">
-        <v>-89476835.98496069</v>
+        <v>-111911249.0019594</v>
       </c>
       <c r="D4" t="n">
-        <v>49444924.03022429</v>
+        <v>55547151.11559548</v>
       </c>
       <c r="E4" t="n">
-        <v>942916.4143896659</v>
+        <v>855710.4823279306</v>
       </c>
       <c r="F4" t="n">
-        <v>-1134934.082252436</v>
+        <v>-1159056.221530605</v>
       </c>
       <c r="G4" t="n">
-        <v>966618.6949263371</v>
+        <v>1147987.178654658</v>
       </c>
       <c r="H4" t="n">
-        <v>-2838565.593454654</v>
+        <v>-3240542.096077707</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-410392.9037308309</v>
+        <v>-468237.0929704851</v>
       </c>
       <c r="C5" t="n">
-        <v>15741702.57410648</v>
+        <v>16344774.50350381</v>
       </c>
       <c r="D5" t="n">
-        <v>942916.4143878605</v>
+        <v>855710.4823316841</v>
       </c>
       <c r="E5" t="n">
-        <v>982978.45994496</v>
+        <v>1070203.214646576</v>
       </c>
       <c r="F5" t="n">
-        <v>24342.18684539068</v>
+        <v>43220.67306816227</v>
       </c>
       <c r="G5" t="n">
-        <v>-74077.02687356112</v>
+        <v>-81632.9182536632</v>
       </c>
       <c r="H5" t="n">
-        <v>-5276.187892717441</v>
+        <v>-4509.43603265702</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1418702.450839928</v>
+        <v>-1421460.028066037</v>
       </c>
       <c r="C6" t="n">
-        <v>6695175.623847375</v>
+        <v>6648185.514450335</v>
       </c>
       <c r="D6" t="n">
-        <v>-1134934.082252652</v>
+        <v>-1159056.221530047</v>
       </c>
       <c r="E6" t="n">
-        <v>24342.18684535557</v>
+        <v>43220.67306824954</v>
       </c>
       <c r="F6" t="n">
-        <v>747842.7102499127</v>
+        <v>748820.2786747159</v>
       </c>
       <c r="G6" t="n">
-        <v>107300.517500436</v>
+        <v>106083.3443256306</v>
       </c>
       <c r="H6" t="n">
-        <v>41833.25559102798</v>
+        <v>40933.88476895314</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>882064.6769767751</v>
+        <v>1050448.297796962</v>
       </c>
       <c r="C7" t="n">
-        <v>-3840600.547944575</v>
+        <v>-4444658.216510372</v>
       </c>
       <c r="D7" t="n">
-        <v>966618.6949266128</v>
+        <v>1147987.178654125</v>
       </c>
       <c r="E7" t="n">
-        <v>-74077.02687352269</v>
+        <v>-81632.91825374325</v>
       </c>
       <c r="F7" t="n">
-        <v>107300.5175004348</v>
+        <v>106083.3443256321</v>
       </c>
       <c r="G7" t="n">
-        <v>66677.42738966159</v>
+        <v>72577.55397030181</v>
       </c>
       <c r="H7" t="n">
-        <v>-71267.17445596625</v>
+        <v>-82481.03830644654</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2580705.562361878</v>
+        <v>-2936361.213969002</v>
       </c>
       <c r="C8" t="n">
-        <v>7957657.046583521</v>
+        <v>8986371.166772723</v>
       </c>
       <c r="D8" t="n">
-        <v>-2838565.593454892</v>
+        <v>-3240542.096077238</v>
       </c>
       <c r="E8" t="n">
-        <v>-5276.18789282717</v>
+        <v>-4509.43603243128</v>
       </c>
       <c r="F8" t="n">
-        <v>41833.25559102369</v>
+        <v>40933.88476897075</v>
       </c>
       <c r="G8" t="n">
-        <v>-71267.17445595423</v>
+        <v>-82481.03830646878</v>
       </c>
       <c r="H8" t="n">
-        <v>178548.4155759323</v>
+        <v>202883.0481396005</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+dmul-lcdm-free.xlsx
+++ b/code/data/combined/cmb+dmul-lcdm-free.xlsx
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44425444.09731483</v>
+        <v>43575294.85649621</v>
       </c>
       <c r="C2" t="n">
-        <v>-148685611.423977</v>
+        <v>-145846347.9145207</v>
       </c>
       <c r="D2" t="n">
-        <v>46689835.9911103</v>
+        <v>45770888.47557165</v>
       </c>
       <c r="E2" t="n">
-        <v>-468237.0929738093</v>
+        <v>-460982.2861886175</v>
       </c>
       <c r="F2" t="n">
-        <v>-1421460.028066205</v>
+        <v>-1413843.634408191</v>
       </c>
       <c r="G2" t="n">
-        <v>1050448.297797226</v>
+        <v>1023557.718755169</v>
       </c>
       <c r="H2" t="n">
-        <v>-2936361.213968822</v>
+        <v>-2876521.124368926</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148685611.4238889</v>
+        <v>-145846347.9144832</v>
       </c>
       <c r="C3" t="n">
-        <v>895782919.2517341</v>
+        <v>876933849.1278561</v>
       </c>
       <c r="D3" t="n">
-        <v>-111911249.0018322</v>
+        <v>-110082289.0535499</v>
       </c>
       <c r="E3" t="n">
-        <v>16344774.50351323</v>
+        <v>16113321.63830177</v>
       </c>
       <c r="F3" t="n">
-        <v>6648185.514448351</v>
+        <v>6575874.493006076</v>
       </c>
       <c r="G3" t="n">
-        <v>-4444658.216509027</v>
+        <v>-4351201.155645087</v>
       </c>
       <c r="H3" t="n">
-        <v>8986371.166766221</v>
+        <v>8808024.179285593</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46689835.99112028</v>
+        <v>45770888.47557551</v>
       </c>
       <c r="C4" t="n">
-        <v>-111911249.0019594</v>
+        <v>-110082289.0536033</v>
       </c>
       <c r="D4" t="n">
-        <v>55547151.11559548</v>
+        <v>54387207.00184419</v>
       </c>
       <c r="E4" t="n">
-        <v>855710.4823279306</v>
+        <v>837194.9054088551</v>
       </c>
       <c r="F4" t="n">
-        <v>-1159056.221530605</v>
+        <v>-1155120.540673981</v>
       </c>
       <c r="G4" t="n">
-        <v>1147987.178654658</v>
+        <v>1119448.476684016</v>
       </c>
       <c r="H4" t="n">
-        <v>-3240542.096077707</v>
+        <v>-3173093.46368802</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-468237.0929704851</v>
+        <v>-460982.2861869388</v>
       </c>
       <c r="C5" t="n">
-        <v>16344774.50350381</v>
+        <v>16113321.63829696</v>
       </c>
       <c r="D5" t="n">
-        <v>855710.4823316841</v>
+        <v>837194.9054107694</v>
       </c>
       <c r="E5" t="n">
-        <v>1070203.214646576</v>
+        <v>1062321.036112378</v>
       </c>
       <c r="F5" t="n">
-        <v>43220.67306816227</v>
+        <v>43141.09559430087</v>
       </c>
       <c r="G5" t="n">
-        <v>-81632.9182536632</v>
+        <v>-81084.23474120072</v>
       </c>
       <c r="H5" t="n">
-        <v>-4509.43603265702</v>
+        <v>-4385.553100379017</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1421460.028066037</v>
+        <v>-1413843.634408175</v>
       </c>
       <c r="C6" t="n">
-        <v>6648185.514450335</v>
+        <v>6575874.493006185</v>
       </c>
       <c r="D6" t="n">
-        <v>-1159056.221530047</v>
+        <v>-1155120.54067385</v>
       </c>
       <c r="E6" t="n">
-        <v>43220.67306824954</v>
+        <v>43141.09559431218</v>
       </c>
       <c r="F6" t="n">
-        <v>748820.2786747159</v>
+        <v>744664.3838415772</v>
       </c>
       <c r="G6" t="n">
-        <v>106083.3443256306</v>
+        <v>105952.2139500339</v>
       </c>
       <c r="H6" t="n">
-        <v>40933.88476895314</v>
+        <v>40551.41764811351</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1050448.297796962</v>
+        <v>1023557.718755006</v>
       </c>
       <c r="C7" t="n">
-        <v>-4444658.216510372</v>
+        <v>-4351201.155645755</v>
       </c>
       <c r="D7" t="n">
-        <v>1147987.178654125</v>
+        <v>1119448.476683716</v>
       </c>
       <c r="E7" t="n">
-        <v>-81632.91825374325</v>
+        <v>-81084.23474125093</v>
       </c>
       <c r="F7" t="n">
-        <v>106083.3443256321</v>
+        <v>105952.2139500326</v>
       </c>
       <c r="G7" t="n">
-        <v>72577.55397030181</v>
+        <v>71670.12459127374</v>
       </c>
       <c r="H7" t="n">
-        <v>-82481.03830644654</v>
+        <v>-80596.34560499355</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2936361.213969002</v>
+        <v>-2876521.124368994</v>
       </c>
       <c r="C8" t="n">
-        <v>8986371.166772723</v>
+        <v>8808024.179288417</v>
       </c>
       <c r="D8" t="n">
-        <v>-3240542.096077238</v>
+        <v>-3173093.463687829</v>
       </c>
       <c r="E8" t="n">
-        <v>-4509.43603243128</v>
+        <v>-4385.553100261974</v>
       </c>
       <c r="F8" t="n">
-        <v>40933.88476897075</v>
+        <v>40551.41764811826</v>
       </c>
       <c r="G8" t="n">
-        <v>-82481.03830646878</v>
+        <v>-80596.34560500689</v>
       </c>
       <c r="H8" t="n">
-        <v>202883.0481396005</v>
+        <v>198605.9734480069</v>
       </c>
     </row>
   </sheetData>
